--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:28:25+00:00</t>
+    <t>2026-07-07T16:30:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:30:55+00:00</t>
+    <t>2026-07-08T14:05:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T14:05:48+00:00</t>
+    <t>2026-07-08T15:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:14:17+00:00</t>
+    <t>2026-07-08T16:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T16:19:56+00:00</t>
+    <t>2026-07-08T16:46:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T16:46:42+00:00</t>
+    <t>2026-07-08T16:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T16:50:32+00:00</t>
+    <t>2026-07-08T16:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T16:54:17+00:00</t>
+    <t>2026-07-08T16:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T16:59:21+00:00</t>
+    <t>2026-07-08T17:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T17:09:23+00:00</t>
+    <t>2026-07-08T17:17:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T17:17:11+00:00</t>
+    <t>2026-07-09T08:06:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T08:06:43+00:00</t>
+    <t>2026-07-09T12:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
+++ b/sg-ml-ror/ig/StructureDefinition-ror-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T12:48:10+00:00</t>
+    <t>2026-07-09T15:33:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
